--- a/docs/downloads/20260808_Seputeh Hills_Teduh Weekly Update.xlsx
+++ b/docs/downloads/20260808_Seputeh Hills_Teduh Weekly Update.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20260808" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="20260808" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/docs/downloads/20260808_Seputeh Hills_Teduh Weekly Update.xlsx
+++ b/docs/downloads/20260808_Seputeh Hills_Teduh Weekly Update.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -510,10 +510,7 @@
     <col width="9" customWidth="1" min="16" max="16"/>
     <col width="9" customWidth="1" min="17" max="17"/>
     <col width="9" customWidth="1" min="18" max="18"/>
-    <col width="9" customWidth="1" min="19" max="19"/>
-    <col width="9" customWidth="1" min="20" max="20"/>
-    <col width="9" customWidth="1" min="21" max="21"/>
-    <col width="42" customWidth="1" min="22" max="22"/>
+    <col width="42" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -540,11 +537,8 @@
       <c r="M3" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="P3" s="3" t="n">
+      <c r="P3" s="4" t="n">
         <v>46241</v>
-      </c>
-      <c r="S3" s="4" t="n">
-        <v>46242</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -625,37 +619,22 @@
           <t>%</t>
         </is>
       </c>
-      <c r="P4" s="5" t="inlineStr">
+      <c r="P4" s="6" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="Q4" s="5" t="inlineStr">
+      <c r="Q4" s="6" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="R4" s="5" t="inlineStr">
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="S4" s="6" t="inlineStr">
-        <is>
-          <t>NEW SALES</t>
-        </is>
-      </c>
-      <c r="T4" s="6" t="inlineStr">
-        <is>
-          <t>TOTAL SOLD</t>
-        </is>
-      </c>
-      <c r="U4" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="V4" s="5" t="inlineStr">
+      <c r="S4" s="5" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
@@ -718,29 +697,18 @@
         <f>N5/$F$5</f>
         <v/>
       </c>
-      <c r="P5" s="10">
+      <c r="P5" s="12">
         <f>Q5-N5</f>
         <v/>
       </c>
-      <c r="Q5" s="10" t="n">
+      <c r="Q5" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="R5" s="11">
+      <c r="R5" s="13">
         <f>Q5/$F$5</f>
         <v/>
       </c>
-      <c r="S5" s="12">
-        <f>T5-Q5</f>
-        <v/>
-      </c>
-      <c r="T5" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="U5" s="13">
-        <f>T5/$F$5</f>
-        <v/>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
+      <c r="S5" s="8" t="inlineStr">
         <is>
           <t>Big unit (5,533 to Penthouse 19,031sqft)</t>
         </is>
@@ -803,29 +771,18 @@
         <f>N6/$F$6</f>
         <v/>
       </c>
-      <c r="P6" s="10">
+      <c r="P6" s="12">
         <f>Q6-N6</f>
         <v/>
       </c>
-      <c r="Q6" s="10" t="n">
+      <c r="Q6" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="R6" s="11">
+      <c r="R6" s="13">
         <f>Q6/$F$6</f>
         <v/>
       </c>
-      <c r="S6" s="12">
-        <f>T6-Q6</f>
-        <v/>
-      </c>
-      <c r="T6" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="U6" s="13">
-        <f>T6/$F$6</f>
-        <v/>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
+      <c r="S6" s="8" t="inlineStr">
         <is>
           <t>Big unit (3,380 to 4,090sqft  &amp; Penthouse 7,459sqft).</t>
         </is>
@@ -888,29 +845,18 @@
         <f>N7/$F$7</f>
         <v/>
       </c>
-      <c r="P7" s="10">
+      <c r="P7" s="12">
         <f>Q7-N7</f>
         <v/>
       </c>
-      <c r="Q7" s="10" t="n">
+      <c r="Q7" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="R7" s="11">
+      <c r="R7" s="13">
         <f>Q7/$F$7</f>
         <v/>
       </c>
-      <c r="S7" s="12">
-        <f>T7-Q7</f>
-        <v/>
-      </c>
-      <c r="T7" s="12" t="n">
-        <v>44</v>
-      </c>
-      <c r="U7" s="13">
-        <f>T7/$F$7</f>
-        <v/>
-      </c>
-      <c r="V7" s="8" t="inlineStr">
+      <c r="S7" s="8" t="inlineStr">
         <is>
           <t>Small unit (452 to 1,679 sq ft)</t>
         </is>
@@ -973,29 +919,18 @@
         <f>N8/$F$8</f>
         <v/>
       </c>
-      <c r="P8" s="10">
+      <c r="P8" s="12">
         <f>Q8-N8</f>
         <v/>
       </c>
-      <c r="Q8" s="10" t="n">
+      <c r="Q8" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="R8" s="11">
+      <c r="R8" s="13">
         <f>Q8/$F$8</f>
         <v/>
       </c>
-      <c r="S8" s="12">
-        <f>T8-Q8</f>
-        <v/>
-      </c>
-      <c r="T8" s="12" t="n">
-        <v>45</v>
-      </c>
-      <c r="U8" s="13">
-        <f>T8/$F$8</f>
-        <v/>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
+      <c r="S8" s="8" t="inlineStr">
         <is>
           <t>4-storey Villa (4,854 to 5,157 sq ft); left 3 bumi units</t>
         </is>
@@ -1058,29 +993,18 @@
         <f>N9/$F$9</f>
         <v/>
       </c>
-      <c r="P9" s="10">
+      <c r="P9" s="12">
         <f>Q9-N9</f>
         <v/>
       </c>
-      <c r="Q9" s="10" t="n">
+      <c r="Q9" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="R9" s="11">
+      <c r="R9" s="13">
         <f>Q9/$F$9</f>
         <v/>
       </c>
-      <c r="S9" s="12">
-        <f>T9-Q9</f>
-        <v/>
-      </c>
-      <c r="T9" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" s="13">
-        <f>T9/$F$9</f>
-        <v/>
-      </c>
-      <c r="V9" s="8" t="inlineStr">
+      <c r="S9" s="8" t="inlineStr">
         <is>
           <t>Big unit (1,648 to 3,856 sq ft)</t>
         </is>
@@ -1133,41 +1057,29 @@
         <f>N10/$F$10</f>
         <v/>
       </c>
-      <c r="P10" s="10">
+      <c r="P10" s="12">
         <f>Q10-N10</f>
         <v/>
       </c>
-      <c r="Q10" s="10" t="n">
+      <c r="Q10" s="12" t="n">
         <v>262</v>
       </c>
-      <c r="R10" s="11">
+      <c r="R10" s="13">
         <f>Q10/$F$10</f>
         <v/>
       </c>
-      <c r="S10" s="12">
-        <f>T10-Q10</f>
-        <v/>
-      </c>
-      <c r="T10" s="12" t="n">
-        <v>271</v>
-      </c>
-      <c r="U10" s="13">
-        <f>T10/$F$10</f>
-        <v/>
-      </c>
-      <c r="V10" s="8" t="inlineStr">
+      <c r="S10" s="8" t="inlineStr">
         <is>
           <t>Big unit (2,842 to 10,613 sq ft)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="S3:U3"/>
-    <mergeCell ref="G3:I3"/>
+  <mergeCells count="4">
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="P3:R3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="M3:O3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
